--- a/graficos/BERT_mejores_diversidad.xlsx
+++ b/graficos/BERT_mejores_diversidad.xlsx
@@ -49,88 +49,88 @@
     <t>comisión_lim</t>
   </si>
   <si>
-    <t>denuncia_bert</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_bert_K5_0.05</t>
-  </si>
-  <si>
-    <t>denuncia</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_K5_0.05</t>
+    <t>antecedentes</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_K5_0.05</t>
+  </si>
+  <si>
+    <t>antecedentes_bert</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_bert_K5_0.05</t>
   </si>
   <si>
     <t>orps_lim</t>
   </si>
   <si>
-    <t>orps_lim_denuncia_K35_0.01</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_K41_0.01</t>
+    <t>orps_lim_antecedentes_K35_0.01</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_K41_0.01</t>
   </si>
   <si>
     <t>comisión</t>
   </si>
   <si>
-    <t>comisión_denuncia_K22_0.01</t>
+    <t>comisión_antecedentes_K22_0.01</t>
   </si>
   <si>
     <t>orps</t>
   </si>
   <si>
-    <t>orps_denuncia_bert_K24_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_bert_K35_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_K6_0.05</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_bert_K32_0.01</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_K45_0.01</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_bert_K6_0.05</t>
+    <t>orps_antecedentes_bert_K24_0.01</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_bert_K35_0.01</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_K6_0.05</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_bert_K32_0.01</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_K45_0.01</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_bert_K6_0.05</t>
   </si>
   <si>
     <t>todos</t>
   </si>
   <si>
-    <t>todos_denuncia_bert_K6_0.05</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen_bert</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_bert_K40_0.01</t>
-  </si>
-  <si>
-    <t>todos_denuncia_K5_0.05</t>
-  </si>
-  <si>
-    <t>todos_denuncia_K17_0.01</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_bert_K15_0.01</t>
-  </si>
-  <si>
-    <t>orps_denuncia_K15_0.01</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_K7_0.05</t>
-  </si>
-  <si>
-    <t>orps_denuncia_bert_K7_0.05</t>
-  </si>
-  <si>
-    <t>orps_denuncia_K7_0.05</t>
+    <t>todos_antecedentes_bert_K6_0.05</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen_bert</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_bert_K40_0.01</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_K5_0.05</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_K17_0.01</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_bert_K15_0.01</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_K15_0.01</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_K7_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_bert_K7_0.05</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_bert_K7_0.05</t>
   </si>
 </sst>
 </file>
@@ -606,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>35</v>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>41</v>
@@ -670,7 +670,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2">
         <v>22</v>
@@ -702,7 +702,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>24</v>
@@ -734,7 +734,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2">
         <v>35</v>
@@ -766,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2">
         <v>6</v>
@@ -798,7 +798,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2">
         <v>32</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2">
         <v>6</v>
@@ -894,7 +894,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2">
         <v>6</v>
@@ -958,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2">
         <v>5</v>
@@ -990,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2">
         <v>17</v>
@@ -1022,7 +1022,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2">
         <v>15</v>
@@ -1054,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2">
         <v>15</v>
@@ -1086,7 +1086,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2">
         <v>7</v>
